--- a/results/Int Task Remove ACC -0.2/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.2/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>-0.0006991257528037623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01514137163741538</v>
+        <v>0.01513505357457954</v>
       </c>
       <c r="F3" t="n">
         <v>-0.0003158529470195648</v>
@@ -1166,10 +1166,10 @@
         <v>0.03018673646798623</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0008563742987246013</v>
+        <v>-0.0008562552733245807</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005866109720606115</v>
+        <v>0.0005831898293989624</v>
       </c>
       <c r="J3" t="n">
         <v>0.03600913926116998</v>
@@ -1184,7 +1184,7 @@
         <v>0.01238614066832818</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0150659706233344</v>
+        <v>0.01506918399094365</v>
       </c>
       <c r="O3" t="n">
         <v>0.01652659922255018</v>
@@ -1196,7 +1196,7 @@
         <v>0.01756813491240518</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01382123801612265</v>
+        <v>0.0138210312739753</v>
       </c>
       <c r="S3" t="n">
         <v>0.2767374079787144</v>
@@ -1208,7 +1208,7 @@
         <v>0.1171280199679533</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005799764617897073</v>
+        <v>0.0005833976044513566</v>
       </c>
       <c r="W3" t="n">
         <v>0.01311372708098628</v>
@@ -1238,7 +1238,7 @@
         <v>0.2240377241263901</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06915544488018402</v>
+        <v>0.06915224180523206</v>
       </c>
       <c r="AG3" t="n">
         <v>0.1050477850640147</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07125188276720525</v>
+        <v>0.07124867969225331</v>
       </c>
       <c r="AK3" t="n">
         <v>0.06300888842123485</v>
@@ -1316,10 +1316,10 @@
         <v>-0.000820729019889006</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01610448061869625</v>
+        <v>0.01610769398630551</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01057986855573401</v>
+        <v>0.01058312885018425</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0002422660096233486</v>
@@ -1355,7 +1355,7 @@
         <v>0.0004122844532836748</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.003651432683538383</v>
+        <v>0.00365786148456699</v>
       </c>
       <c r="BT3" t="n">
         <v>0.001409107679556992</v>
@@ -1364,7 +1364,7 @@
         <v>0.04694766811727123</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001704014970831571</v>
+        <v>-0.001700811895879618</v>
       </c>
       <c r="BW3" t="n">
         <v>0.009177384974500866</v>
@@ -1373,10 +1373,10 @@
         <v>0.0002258790877187367</v>
       </c>
       <c r="BY3" t="n">
+        <v>0.000363634487719936</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0.0003605308253983974</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.000363634487719936</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0004972039530104666</v>
@@ -1385,7 +1385,7 @@
         <v>0.001775172582309757</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.003564924205685046</v>
+        <v>0.003561682714599145</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0004560385099281471</v>
@@ -1428,7 +1428,7 @@
         <v>0.03497627784486835</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03647922000989064</v>
+        <v>0.03647836439010346</v>
       </c>
       <c r="F4" t="n">
         <v>0.008231870011608746</v>
@@ -1437,10 +1437,10 @@
         <v>0.06746397325432815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006657389373763529</v>
+        <v>0.006658784287046806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001301988260541619</v>
+        <v>0.001298747673729768</v>
       </c>
       <c r="J4" t="n">
         <v>0.05725440815308961</v>
@@ -1455,7 +1455,7 @@
         <v>0.02172775903689566</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03018643041935827</v>
+        <v>0.03019481592506203</v>
       </c>
       <c r="O4" t="n">
         <v>0.0473807396306232</v>
@@ -1467,7 +1467,7 @@
         <v>0.02063492766055205</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02765628064563204</v>
+        <v>0.02766122605287517</v>
       </c>
       <c r="S4" t="n">
         <v>0.1441627710874467</v>
@@ -1479,7 +1479,7 @@
         <v>0.0959605527821334</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001300036686535108</v>
+        <v>0.001303283440645302</v>
       </c>
       <c r="W4" t="n">
         <v>0.02368337143955754</v>
@@ -1509,7 +1509,7 @@
         <v>0.1041513457366417</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06613728386048011</v>
+        <v>0.06613047081237629</v>
       </c>
       <c r="AG4" t="n">
         <v>0.05880184163820042</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.08408055830514512</v>
+        <v>0.08408009046254888</v>
       </c>
       <c r="AK4" t="n">
         <v>0.06980111878292654</v>
@@ -1587,10 +1587,10 @@
         <v>0.005892148075579637</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.03411183984682543</v>
+        <v>0.03411488112430403</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03558603307875292</v>
+        <v>0.03557925445470696</v>
       </c>
       <c r="BH4" t="n">
         <v>0.001273882790609709</v>
@@ -1626,7 +1626,7 @@
         <v>0.009629328731498693</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01097854004856525</v>
+        <v>0.01098044943826951</v>
       </c>
       <c r="BT4" t="n">
         <v>0.00175134686071399</v>
@@ -1635,7 +1635,7 @@
         <v>0.05544497290447495</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01652814277031165</v>
+        <v>0.01652602280072658</v>
       </c>
       <c r="BW4" t="n">
         <v>0.03189669693101058</v>
@@ -1644,10 +1644,10 @@
         <v>0.0005551303607393501</v>
       </c>
       <c r="BY4" t="n">
+        <v>0.000821046844789113</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>0.0008201555323182171</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.000821046844789113</v>
       </c>
       <c r="CA4" t="n">
         <v>0.001574923330591215</v>
@@ -1656,7 +1656,7 @@
         <v>0.005732588659920439</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01111580665476279</v>
+        <v>0.01112274085136548</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004365790014088473</v>
@@ -1699,7 +1699,7 @@
         <v>-0.06455655526992289</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03367909238249599</v>
+        <v>-0.03367909238249598</v>
       </c>
       <c r="F5" t="n">
         <v>-0.01387358184764996</v>
@@ -1861,7 +1861,7 @@
         <v>-0.03812439574605227</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02567260940032419</v>
+        <v>-0.02560777957860619</v>
       </c>
       <c r="BH5" t="n">
         <v>-0.00188162846390697</v>
@@ -1927,7 +1927,7 @@
         <v>-0.001815235008103777</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01782820097244737</v>
+        <v>-0.01786061588330638</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.007541899441340727</v>
@@ -2177,7 +2177,7 @@
         <v>0.01193542075998175</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.00999688391292162</v>
+        <v>-0.009972860850781973</v>
       </c>
       <c r="BW6" t="n">
         <v>-0.0002999000333221979</v>
@@ -2241,7 +2241,7 @@
         <v>0.001121076233183816</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01528776377650292</v>
+        <v>0.01527224546489522</v>
       </c>
       <c r="F7" t="n">
         <v>-0.001118144921005815</v>
@@ -2250,7 +2250,7 @@
         <v>0.005773066412479854</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005911870305487122</v>
+        <v>0.0005756687189410192</v>
       </c>
       <c r="I7" t="n">
         <v>0.0008037106534293126</v>
@@ -2512,7 +2512,7 @@
         <v>0.01688622466133568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03187955880664917</v>
+        <v>0.03187152280536341</v>
       </c>
       <c r="F8" t="n">
         <v>0.003370090168578241</v>
@@ -2521,10 +2521,10 @@
         <v>0.04547136685395126</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003221717497408186</v>
+        <v>0.003245887655319879</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0015422477849903</v>
+        <v>0.00151658921502793</v>
       </c>
       <c r="J8" t="n">
         <v>0.07830439691868671</v>
@@ -2551,7 +2551,7 @@
         <v>0.02740264417691193</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02807064309219977</v>
+        <v>0.02809475109605705</v>
       </c>
       <c r="S8" t="n">
         <v>0.3694666880204996</v>
@@ -2563,7 +2563,7 @@
         <v>0.1826929495319324</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00151658921502793</v>
+        <v>0.0015422477849903</v>
       </c>
       <c r="W8" t="n">
         <v>0.01767598184754709</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.08777279556082504</v>
+        <v>0.08776478787344516</v>
       </c>
       <c r="AK8" t="n">
         <v>0.07226371928717695</v>
@@ -2671,10 +2671,10 @@
         <v>0.0003968117523067083</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.03855291952935881</v>
+        <v>0.03857701978642823</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.007534600383721928</v>
+        <v>0.007526543664418028</v>
       </c>
       <c r="BH8" t="n">
         <v>0.0001278744665021009</v>
@@ -2710,7 +2710,7 @@
         <v>0.0006429997257815595</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.007207253944128811</v>
+        <v>0.007223325946700329</v>
       </c>
       <c r="BT8" t="n">
         <v>0.002600649206200614</v>
@@ -2728,10 +2728,10 @@
         <v>0.0003806401605388976</v>
       </c>
       <c r="BY8" t="n">
+        <v>0.000627885203066178</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>0.0006201260472623316</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.000627885203066178</v>
       </c>
       <c r="CA8" t="n">
         <v>0.001806915838556686</v>
@@ -2810,7 +2810,7 @@
         <v>0.05117325618772102</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08595758354755785</v>
+        <v>0.0859897172236504</v>
       </c>
       <c r="O9" t="n">
         <v>0.09881105398457582</v>
@@ -2864,7 +2864,7 @@
         <v>0.3891415759128763</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1957719410634208</v>
+        <v>0.1957399103139013</v>
       </c>
       <c r="AG9" t="n">
         <v>0.1851173256187721</v>
